--- a/data/trans_dic/P3A$yo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,09; 75,48</t>
+          <t>67,09; 75,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,62; 94,12</t>
+          <t>88,64; 94,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,16; 83,26</t>
+          <t>78,59; 83,59</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,45; 74,25</t>
+          <t>64,48; 73,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,09; 96,28</t>
+          <t>91,1; 96,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,06; 83,58</t>
+          <t>77,64; 83,46</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 67,89</t>
+          <t>16,41; 67,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,14; 94,68</t>
+          <t>84,98; 94,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,86; 74,25</t>
+          <t>24,25; 74,34</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,21; 70,22</t>
+          <t>64,23; 70,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,13; 97,99</t>
+          <t>94,14; 97,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,43; 86,89</t>
+          <t>78,47; 87,33</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,15; 67,04</t>
+          <t>56,81; 66,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,17</t>
+          <t>93,14; 96,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,53; 86,01</t>
+          <t>80,62; 86,51</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,16; 59,08</t>
+          <t>36,28; 57,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,62; 83,61</t>
+          <t>77,35; 83,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,61; 76,24</t>
+          <t>69,03; 76,51</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,81; 66,34</t>
+          <t>43,51; 66,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90,35; 93,27</t>
+          <t>90,3; 93,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66,4; 80,22</t>
+          <t>67,27; 80,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>338965; 381336</t>
+          <t>338950; 380685</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>395936; 420512</t>
+          <t>396025; 421260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>744026; 792634</t>
+          <t>748144; 795793</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>291153; 335408</t>
+          <t>291292; 333847</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>348495; 368329</t>
+          <t>348532; 367853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>651285; 697309</t>
+          <t>647732; 696309</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99734; 453657</t>
+          <t>109684; 453787</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141628; 157492</t>
+          <t>141368; 157380</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182404; 619699</t>
+          <t>202352; 620429</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>664453; 726619</t>
+          <t>664665; 731240</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>920687; 958394</t>
+          <t>920824; 957085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1578783; 1748980</t>
+          <t>1579451; 1757817</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>271475; 318461</t>
+          <t>269891; 315728</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>784781; 809097</t>
+          <t>783655; 807936</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1060106; 1132236</t>
+          <t>1061203; 1138782</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89370; 142100</t>
+          <t>87267; 138762</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>590994; 636590</t>
+          <t>588929; 636595</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>687410; 763855</t>
+          <t>691627; 766542</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1579960; 2239304</t>
+          <t>1468582; 2249215</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3231401; 3335644</t>
+          <t>3229627; 3328191</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4616227; 5577279</t>
+          <t>4676427; 5565956</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$yo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,09; 75,35</t>
+          <t>67,06; 75,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,64; 94,29</t>
+          <t>89,26; 94,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,59; 83,59</t>
+          <t>78,17; 83,42</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,48; 73,9</t>
+          <t>64,85; 73,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,1; 96,15</t>
+          <t>91,32; 96,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,64; 83,46</t>
+          <t>77,98; 83,53</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 67,91</t>
+          <t>60,46; 69,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,98; 94,61</t>
+          <t>85,06; 94,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,25; 74,34</t>
+          <t>68,42; 75,66</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,23; 70,66</t>
+          <t>63,55; 69,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,14; 97,85</t>
+          <t>93,33; 96,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,47; 87,33</t>
+          <t>76,69; 80,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,81; 66,46</t>
+          <t>58,35; 67,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,14; 96,03</t>
+          <t>92,82; 95,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,62; 86,51</t>
+          <t>79,24; 83,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,28; 57,7</t>
+          <t>35,09; 54,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,35; 83,61</t>
+          <t>77,78; 83,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,03; 76,51</t>
+          <t>69,07; 76,43</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,51; 66,63</t>
+          <t>63,68; 67,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90,3; 93,06</t>
+          <t>89,69; 91,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67,27; 80,06</t>
+          <t>77,21; 79,48</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>361000</t>
+          <t>392403</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>410776</t>
+          <t>449313</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>771776</t>
+          <t>841715</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>338950; 380685</t>
+          <t>369266; 413799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>396025; 421260</t>
+          <t>435361; 460485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>748144; 795793</t>
+          <t>811652; 866176</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>313528</t>
+          <t>335066</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>359996</t>
+          <t>398221</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>673524</t>
+          <t>733287</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>291292; 333847</t>
+          <t>313046; 356674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>348532; 367853</t>
+          <t>386415; 406390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>647732; 696309</t>
+          <t>706385; 756698</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>281530</t>
+          <t>306191</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>476449</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>109684; 453787</t>
+          <t>285141; 327254</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141368; 157380</t>
+          <t>158993; 176688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202352; 620429</t>
+          <t>450598; 498268</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>755615</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>937664</t>
+          <t>816354</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1636174</t>
+          <t>1571969</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>664665; 731240</t>
+          <t>719293; 788114</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>920824; 957085</t>
+          <t>803762; 828443</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1579451; 1757817</t>
+          <t>1528568; 1609330</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>294938</t>
+          <t>355993</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>796658</t>
+          <t>782244</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1091596</t>
+          <t>1138237</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>269891; 315728</t>
+          <t>331387; 380813</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>783655; 807936</t>
+          <t>771195; 791497</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1061203; 1138782</t>
+          <t>1108476; 1166959</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>113863</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>616204</t>
+          <t>683574</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>730067</t>
+          <t>789217</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>87267; 138762</t>
+          <t>83232; 128102</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>588929; 636595</t>
+          <t>656695; 709123</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>691627; 766542</t>
+          <t>746972; 826605</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2063371</t>
+          <t>2250911</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3272981</t>
+          <t>3299966</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5336351</t>
+          <t>5550875</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1468582; 2249215</t>
+          <t>2191844; 2315368</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3229627; 3328191</t>
+          <t>3259600; 3334112</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4676427; 5565956</t>
+          <t>5463609; 5624402</t>
         </is>
       </c>
     </row>
